--- a/artfynd/A 43219-2023 artfynd.xlsx
+++ b/artfynd/A 43219-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -781,6 +781,116 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>Ecogain - artinventeringar inför täktansökan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128325230</v>
+      </c>
+      <c r="B3" t="n">
+        <v>106315</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Artrik vägkant, Gtl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>712689</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6400294</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Lokrume</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>norraYSMika Thunell</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Magnus Stenmark</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Via Magnus Stenmark</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 43219-2023 artfynd.xlsx
+++ b/artfynd/A 43219-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>128325230</v>
       </c>
       <c r="B3" t="n">
-        <v>106315</v>
+        <v>106320</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 43219-2023 artfynd.xlsx
+++ b/artfynd/A 43219-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>128325230</v>
       </c>
       <c r="B3" t="n">
-        <v>106320</v>
+        <v>106413</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 43219-2023 artfynd.xlsx
+++ b/artfynd/A 43219-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>128325230</v>
       </c>
       <c r="B3" t="n">
-        <v>106413</v>
+        <v>106435</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 43219-2023 artfynd.xlsx
+++ b/artfynd/A 43219-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>128325230</v>
       </c>
       <c r="B3" t="n">
-        <v>106435</v>
+        <v>106447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 43219-2023 artfynd.xlsx
+++ b/artfynd/A 43219-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>128325230</v>
       </c>
       <c r="B3" t="n">
-        <v>106447</v>
+        <v>106456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 43219-2023 artfynd.xlsx
+++ b/artfynd/A 43219-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>128325230</v>
       </c>
       <c r="B3" t="n">
-        <v>106456</v>
+        <v>106461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 43219-2023 artfynd.xlsx
+++ b/artfynd/A 43219-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>128325230</v>
       </c>
       <c r="B3" t="n">
-        <v>106461</v>
+        <v>106489</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 43219-2023 artfynd.xlsx
+++ b/artfynd/A 43219-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>128325230</v>
       </c>
       <c r="B3" t="n">
-        <v>106489</v>
+        <v>106502</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 43219-2023 artfynd.xlsx
+++ b/artfynd/A 43219-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>128325230</v>
       </c>
       <c r="B3" t="n">
-        <v>106502</v>
+        <v>106506</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 43219-2023 artfynd.xlsx
+++ b/artfynd/A 43219-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115886454</v>
+        <v>106442304</v>
       </c>
       <c r="B2" t="n">
-        <v>56577</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106341</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100038</v>
+        <v>671</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Gotlandsmåra</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Galium rotundifolium</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kalvskogshajd, Gtl</t>
+          <t>Lauks 550 m S, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>712832</v>
+        <v>712748</v>
       </c>
       <c r="R2" t="n">
-        <v>6400540</v>
+        <v>6400568</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,12 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-06-06</t>
+          <t>1993-01-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-06-06</t>
+          <t>1997-12-31</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>.  Samfällt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,68 +765,69 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kaj Svahn</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
+          <t>Lars-Åke Pettersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Ecogain - artinventeringar inför täktansökan</t>
+          <t>Projekt Gotlands Flora</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128325230</v>
+        <v>115886454</v>
       </c>
       <c r="B3" t="n">
-        <v>106506</v>
+        <v>57247</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221903</v>
+        <v>100038</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Artrik vägkant, Gtl</t>
+          <t>Kalvskogshajd, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>712689</v>
+        <v>712832</v>
       </c>
       <c r="R3" t="n">
-        <v>6400294</v>
+        <v>6400540</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -855,17 +851,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2023-06-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>norraYSMika Thunell</t>
+          <t>2023-06-06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -880,15 +871,125 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Kaj Svahn</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Ecogain - artinventeringar inför täktansökan</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128325230</v>
+      </c>
+      <c r="B4" t="n">
+        <v>107061</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Artrik vägkant, Gtl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>712689</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6400294</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lokrume</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>norraYSMika Thunell</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Magnus Stenmark</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Via Magnus Stenmark</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>

--- a/artfynd/A 43219-2023 artfynd.xlsx
+++ b/artfynd/A 43219-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106442304</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
           <t>Ecogain - artinventeringar inför täktansökan</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115886454</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -994,8 +1009,18 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128325230</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>